--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/MonsterCorpseLootConfig.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/MonsterCorpseLootConfig.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -93,6 +93,15 @@
   </si>
   <si>
     <t>22001*1|20002*1|21001*1</t>
+  </si>
+  <si>
+    <t>22001*1|20002*1</t>
+  </si>
+  <si>
+    <t>22001*1|20001*1|20002*1</t>
+  </si>
+  <si>
+    <t>22001*2|20001*1|20002*1|21001*1</t>
   </si>
 </sst>
 </file>
@@ -138,7 +147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -309,6 +318,136 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="B7" s="0">
+        <v>3</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="0">
+        <v>1012</v>
+      </c>
+      <c r="E7" s="0">
+        <v>1002</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0">
+        <v>2</v>
+      </c>
+      <c r="I7" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0">
+        <v>4</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="0">
+        <v>1013</v>
+      </c>
+      <c r="E8" s="0">
+        <v>1002</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="0">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0">
+        <v>2</v>
+      </c>
+      <c r="I8" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0">
+        <v>5</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="0">
+        <v>1014</v>
+      </c>
+      <c r="E9" s="0">
+        <v>1002</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="0">
+        <v>1</v>
+      </c>
+      <c r="H9" s="0">
+        <v>2</v>
+      </c>
+      <c r="I9" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0">
+        <v>6</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="0">
+        <v>1015</v>
+      </c>
+      <c r="E10" s="0">
+        <v>1002</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="0">
+        <v>2</v>
+      </c>
+      <c r="H10" s="0">
+        <v>2</v>
+      </c>
+      <c r="I10" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0">
+        <v>7</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1016</v>
+      </c>
+      <c r="E11" s="0">
+        <v>1002</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="0">
+        <v>2</v>
+      </c>
+      <c r="H11" s="0">
+        <v>3</v>
+      </c>
+      <c r="I11" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
